--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2785.64</v>
+        <v>2696.81</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3708.29</v>
+        <v>3590.04</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2973.24</v>
+        <v>2878.43</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>890.08</v>
+        <v>861.7</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3351.51</v>
+        <v>3244.64</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1558.83</v>
+        <v>1509.12</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2915.35</v>
+        <v>2822.39</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1687.47</v>
+        <v>1633.66</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>778.64</v>
+        <v>753.8099999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1457.17</v>
+        <v>1410.7</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1095.47</v>
+        <v>1060.54</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>800.5</v>
+        <v>774.98</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1360.43</v>
+        <v>1317.05</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1852.64</v>
+        <v>1793.56</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>951.16</v>
+        <v>920.83</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3421.63</v>
+        <v>3312.53</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1372.05</v>
+        <v>1328.3</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1442.52</v>
+        <v>1396.52</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>795.1900000000001</v>
+        <v>769.84</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1179.43</v>
+        <v>1141.82</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8841.91</v>
+        <v>8559.969999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1668.55</v>
+        <v>1615.35</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32924.08</v>
+        <v>31874.23</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1193.55</v>
+        <v>1155.5</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2930.27</v>
+        <v>2836.83</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5954.13</v>
+        <v>5764.27</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2902.97</v>
+        <v>2810.41</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5044.76</v>
+        <v>4883.89</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1547.61</v>
+        <v>1498.26</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2439.4</v>
+        <v>2361.62</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1090.59</v>
+        <v>1055.81</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2127.33</v>
+        <v>2059.5</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2445.11</v>
+        <v>2367.14</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1791.32</v>
+        <v>1734.2</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4362.27</v>
+        <v>4223.17</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1069.15</v>
+        <v>1035.06</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2075.47</v>
+        <v>2009.29</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>787.13</v>
+        <v>762.03</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2547.03</v>
+        <v>2465.81</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5343.75</v>
+        <v>5173.36</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>787.46</v>
+        <v>762.35</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2526.88</v>
+        <v>2446.31</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>15937.91</v>
+        <v>15429.7</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>852.77</v>
+        <v>825.58</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>10548.49</v>
+        <v>10340.46</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6854.37</v>
+        <v>6719.19</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>779.1</v>
+        <v>763.74</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2010.14</v>
+        <v>1970.49</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>791.3099999999999</v>
+        <v>775.71</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1495.57</v>
+        <v>1466.08</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>791.08</v>
+        <v>775.48</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1273.32</v>
+        <v>1248.21</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3395.38</v>
+        <v>3328.41</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>827.41</v>
+        <v>811.09</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1211.17</v>
+        <v>1187.28</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1640.82</v>
+        <v>1608.46</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>919.54</v>
+        <v>901.41</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5773.43</v>
+        <v>5659.57</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>904.21</v>
+        <v>886.38</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1719.22</v>
+        <v>1685.32</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>794.96</v>
+        <v>779.28</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1688.26</v>
+        <v>1654.96</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>856.54</v>
+        <v>839.65</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1897.56</v>
+        <v>1860.14</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>780.3200000000001</v>
+        <v>764.9400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1599.85</v>
+        <v>1568.3</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1603.72</v>
+        <v>1572.09</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1468.1</v>
+        <v>1439.15</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4743.37</v>
+        <v>4649.83</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3144.09</v>
+        <v>3082.09</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2063.68</v>
+        <v>2022.98</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>923.36</v>
+        <v>905.15</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6010.92</v>
+        <v>5892.38</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1765.4</v>
+        <v>1730.58</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>787.25</v>
+        <v>771.72</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1003.54</v>
+        <v>983.75</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>15573.47</v>
+        <v>15266.34</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4631.4</v>
+        <v>4540.06</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2179.18</v>
+        <v>2136.21</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5198.83</v>
+        <v>5061.92</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3438.45</v>
+        <v>3347.9</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4313.97</v>
+        <v>4200.36</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>929.33</v>
+        <v>904.86</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1053.9</v>
+        <v>1026.14</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1202.74</v>
+        <v>1171.07</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2371.69</v>
+        <v>2309.23</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1422.35</v>
+        <v>1384.89</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>974.8099999999999</v>
+        <v>949.14</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3060.83</v>
+        <v>2980.23</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>868.04</v>
+        <v>845.1799999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>894.6</v>
+        <v>871.04</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4105.62</v>
+        <v>3997.51</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1594.38</v>
+        <v>1552.39</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>890.05</v>
+        <v>866.61</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>76505.8</v>
+        <v>74491.14999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2014.31</v>
+        <v>1961.27</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1087.83</v>
+        <v>1059.19</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2112.6</v>
+        <v>2056.97</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1652.55</v>
+        <v>1609.03</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1336.45</v>
+        <v>1301.26</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1102.83</v>
+        <v>1073.79</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1670.24</v>
+        <v>1626.26</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2979.5</v>
+        <v>2901.04</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>796.13</v>
+        <v>775.16</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>785.63</v>
+        <v>764.9400000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3018.58</v>
+        <v>2963.84</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>141349.08</v>
+        <v>138785.74</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1950.89</v>
+        <v>1915.51</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>900.21</v>
+        <v>883.89</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>780.4400000000001</v>
+        <v>766.29</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2787.97</v>
+        <v>2737.42</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>783.8099999999999</v>
+        <v>769.6</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1888.71</v>
+        <v>1854.46</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1489.15</v>
+        <v>1462.14</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1237.29</v>
+        <v>1214.85</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2262.51</v>
+        <v>2221.48</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1058.88</v>
+        <v>1039.68</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>32768.12</v>
+        <v>32173.87</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1538.45</v>
+        <v>1510.55</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1101.83</v>
+        <v>1081.85</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2464.09</v>
+        <v>2419.4</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1780.29</v>
+        <v>1748.01</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1734.2</v>
+        <v>1702.75</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>792.26</v>
+        <v>777.89</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>815.78</v>
+        <v>800.99</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2733.83</v>
+        <v>2684.26</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1557.47</v>
+        <v>1529.23</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>778.96</v>
+        <v>764.84</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2062.1</v>
+        <v>2024.7</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1947.65</v>
+        <v>1912.33</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1111.1</v>
+        <v>1090.95</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>922.12</v>
+        <v>905.39</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2166.92</v>
+        <v>2127.63</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1426.94</v>
+        <v>1401.06</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3373.52</v>
+        <v>3312.35</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2658.28</v>
+        <v>2610.07</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>7486.25</v>
+        <v>7285.79</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>12362.47</v>
+        <v>12031.44</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>782.95</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3234.73</v>
+        <v>3148.11</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>954.9</v>
+        <v>929.33</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3581.47</v>
+        <v>3485.57</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>7780.19</v>
+        <v>7571.87</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>932.51</v>
+        <v>907.54</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4013.51</v>
+        <v>3906.04</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>778.98</v>
+        <v>758.12</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1672.48</v>
+        <v>1627.7</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2896.89</v>
+        <v>2819.32</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>4594.22</v>
+        <v>4471.2</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>812.88</v>
+        <v>791.12</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>855.37</v>
+        <v>832.47</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>12509.29</v>
+        <v>12174.33</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1777.78</v>
+        <v>1730.18</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>778.46</v>
+        <v>757.62</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>791.85</v>
+        <v>770.64</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>939.4</v>
+        <v>914.24</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1414.33</v>
+        <v>1376.46</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>904.9299999999999</v>
+        <v>880.6900000000001</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1612.81</v>
+        <v>1569.62</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>779.75</v>
+        <v>758.88</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7049.39</v>
+        <v>6860.64</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1097.83</v>
+        <v>1068.43</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3367.56</v>
+        <v>3277.39</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1287.64</v>
+        <v>1253.16</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1801.02</v>
+        <v>1752.8</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2032.53</v>
+        <v>1978.11</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1289.78</v>
+        <v>1255.24</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1970.38</v>
+        <v>1917.62</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1640.12</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>993.33</v>
+        <v>966.74</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>779.73</v>
+        <v>758.85</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5633.3</v>
+        <v>5482.46</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>6254.26</v>
+        <v>6086.79</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1051.06</v>
+        <v>1022.92</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>20722.99</v>
+        <v>20168.1</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1067.52</v>
+        <v>1038.93</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1326.77</v>
+        <v>1291.25</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4102.23</v>
+        <v>3992.39</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>976.9</v>
+        <v>950.75</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>854.3099999999999</v>
+        <v>831.4400000000001</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>886.98</v>
+        <v>889.5599999999999</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>7904.03</v>
+        <v>7927.04</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>959.28</v>
+        <v>962.0700000000001</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2169.96</v>
+        <v>2176.28</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>796.34</v>
+        <v>798.66</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2025.5</v>
+        <v>2031.4</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1015.73</v>
+        <v>1018.69</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8422.92</v>
+        <v>8447.440000000001</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>830.26</v>
+        <v>832.67</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>820.72</v>
+        <v>823.1</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1113.45</v>
+        <v>1116.69</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>833.41</v>
+        <v>835.84</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1839.56</v>
+        <v>1844.92</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2534.51</v>
+        <v>2541.89</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5075.82</v>
+        <v>5090.59</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1045.38</v>
+        <v>1048.43</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7968.87</v>
+        <v>7992.07</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>798.1799999999999</v>
+        <v>800.51</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1243.16</v>
+        <v>1246.78</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>4276.87</v>
+        <v>4289.32</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>9942.129999999999</v>
+        <v>9971.07</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6032.66</v>
+        <v>6050.22</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>12473.22</v>
+        <v>12509.53</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1085.45</v>
+        <v>1088.61</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>858.04</v>
+        <v>860.54</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>821.11</v>
+        <v>823.5</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>911.7</v>
+        <v>915.49</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>822.3099999999999</v>
+        <v>825.72</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4448.62</v>
+        <v>4467.11</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2821.21</v>
+        <v>2832.94</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1038.77</v>
+        <v>1043.09</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4966.03</v>
+        <v>4986.67</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>8488.66</v>
+        <v>8523.940000000001</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>7811.17</v>
+        <v>7843.64</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1342.4</v>
+        <v>1347.98</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>779.16</v>
+        <v>782.4</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3530.02</v>
+        <v>3544.69</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>803.27</v>
+        <v>806.61</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4604.21</v>
+        <v>4623.35</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1090.15</v>
+        <v>1094.69</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2402.19</v>
+        <v>2412.18</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1390.92</v>
+        <v>1396.7</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1478.08</v>
+        <v>1484.22</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1975.68</v>
+        <v>1983.89</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1314.27</v>
+        <v>1319.73</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3647.32</v>
+        <v>3662.48</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1461.81</v>
+        <v>1467.88</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1597.8</v>
+        <v>1604.44</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>27735.28</v>
+        <v>27850.55</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2487.39</v>
+        <v>2497.73</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>15265.27</v>
+        <v>15328.71</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2975.05</v>
+        <v>2987.41</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1938.11</v>
+        <v>1946.17</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1111.59</v>
+        <v>1116.21</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1074.69</v>
+        <v>1079.16</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>781.0599999999999</v>
+        <v>784.3099999999999</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3228.78</v>
+        <v>3242.2</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1743.35</v>
+        <v>1750.59</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2657.43</v>
+        <v>2668.48</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1746.28</v>
+        <v>1753.54</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1797.62</v>
+        <v>1805.09</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>34061.84</v>
+        <v>34203.4</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2594.7</v>
+        <v>2605.48</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1498.43</v>
+        <v>1504.66</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>791.52</v>
+        <v>798.23</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1438.11</v>
+        <v>1450.31</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1543.55</v>
+        <v>1556.65</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>813.23</v>
+        <v>820.13</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1683.69</v>
+        <v>1697.98</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>829.38</v>
+        <v>836.42</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1717.28</v>
+        <v>1731.85</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>933.5700000000001</v>
+        <v>941.49</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>807.84</v>
+        <v>814.7</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>779.14</v>
+        <v>785.75</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>14740.84</v>
+        <v>14865.94</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1720.03</v>
+        <v>1734.62</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>833.14</v>
+        <v>840.21</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>859.46</v>
+        <v>866.76</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1833.07</v>
+        <v>1848.63</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2242.8</v>
+        <v>2261.83</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3342.97</v>
+        <v>3371.34</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3298.73</v>
+        <v>3326.73</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>945.73</v>
+        <v>953.75</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2226.56</v>
+        <v>2245.46</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1900</v>
+        <v>1916.13</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2041.28</v>
+        <v>2058.61</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1109.01</v>
+        <v>1118.42</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1515.28</v>
+        <v>1528.14</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>6399.06</v>
+        <v>6453.36</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2761.33</v>
+        <v>2784.77</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>5163.52</v>
+        <v>5207.34</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>44218.56</v>
+        <v>44593.84</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>867.6799999999999</v>
+        <v>875.05</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1892.03</v>
+        <v>1908.09</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1676.28</v>
+        <v>1690.51</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1676.28</v>
+        <v>1690.51</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>828.0700000000001</v>
+        <v>835.1</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2542.57</v>
+        <v>2564.15</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>9473.629999999999</v>
+        <v>9554.030000000001</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>5227.73</v>
+        <v>5272.1</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2252.41</v>
+        <v>2271.52</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1030.74</v>
+        <v>1039.49</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>816.28</v>
+        <v>823.2</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>3546.6</v>
+        <v>3576.7</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>784.51</v>
+        <v>791.16</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>809.35</v>
+        <v>816.22</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1075.46</v>
+        <v>1073.66</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1960.22</v>
+        <v>1956.94</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2725.89</v>
+        <v>2721.33</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>7336.77</v>
+        <v>7324.5</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>19747.49</v>
+        <v>19714.47</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1431.36</v>
+        <v>1428.97</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>890.29</v>
+        <v>888.8099999999999</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1170.67</v>
+        <v>1168.71</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>4961.39</v>
+        <v>4953.1</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1429.37</v>
+        <v>1426.98</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3283.83</v>
+        <v>3278.34</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2226.56</v>
+        <v>2222.84</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>811.74</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2504.74</v>
+        <v>2500.55</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2003.91</v>
+        <v>2000.56</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>6324.5</v>
+        <v>6313.92</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1590.93</v>
+        <v>1588.27</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3391.73</v>
+        <v>3386.06</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3246.28</v>
+        <v>3240.85</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2714.37</v>
+        <v>2709.83</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1168.91</v>
+        <v>1166.95</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3942.76</v>
+        <v>3936.16</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5155.55</v>
+        <v>5146.93</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1144.95</v>
+        <v>1143.03</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3681.6</v>
+        <v>3675.44</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2763.7</v>
+        <v>2759.08</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2252.87</v>
+        <v>2249.1</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>780.95</v>
+        <v>779.65</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2369.7</v>
+        <v>2365.74</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2084.09</v>
+        <v>2080.6</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3135.52</v>
+        <v>3130.28</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1656.78</v>
+        <v>1677.17</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>4465.32</v>
+        <v>4520.27</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>8114.49</v>
+        <v>8214.35</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1696.69</v>
+        <v>1717.58</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>8321.530000000001</v>
+        <v>8423.940000000001</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>3823.46</v>
+        <v>3870.52</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>914.04</v>
+        <v>925.29</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1881.17</v>
+        <v>1904.32</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>998.1</v>
+        <v>1010.38</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1314.7</v>
+        <v>1330.88</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3904.01</v>
+        <v>3952.06</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2115.57</v>
+        <v>2141.6</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2369.04</v>
+        <v>2398.19</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>3150.23</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2426.95</v>
+        <v>2456.82</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>946.5700000000001</v>
+        <v>958.22</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>4163.54</v>
+        <v>4214.78</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>6393.95</v>
+        <v>6472.64</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>790.8099999999999</v>
+        <v>800.54</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1064.58</v>
+        <v>1077.68</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>781.52</v>
+        <v>791.14</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>923.28</v>
+        <v>934.64</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3178.44</v>
+        <v>3217.56</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>19164.34</v>
+        <v>19400.21</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1829.36</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>7003.6</v>
+        <v>7089.79</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>12224.5</v>
+        <v>12374.95</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>6454.28</v>
+        <v>6533.71</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>7941.14</v>
+        <v>8038.88</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>795.73</v>
+        <v>805.52</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>864.84</v>
+        <v>875.48</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>28814.4</v>
+        <v>29169.02</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>10552.05</v>
+        <v>10681.92</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>780.77</v>
+        <v>790.38</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2482.17</v>
+        <v>2512.72</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>821.8</v>
+        <v>831.91</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3034.22</v>
+        <v>3071.56</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>35247.97</v>
+        <v>35681.78</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6413.6</v>
+        <v>6492.53</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>5423.27</v>
+        <v>5490.02</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2144.06</v>
+        <v>2170.45</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1205.58</v>
+        <v>1221.62</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1178.96</v>
+        <v>1194.66</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>6678.75</v>
+        <v>6767.67</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>905.87</v>
+        <v>917.9299999999999</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>3188.42</v>
+        <v>3230.86</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>2292.51</v>
+        <v>2323.03</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>821.95</v>
+        <v>832.89</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>4446.51</v>
+        <v>4505.71</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>12575.97</v>
+        <v>12743.39</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1485.64</v>
+        <v>1505.42</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1170.04</v>
+        <v>1185.62</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1009.91</v>
+        <v>1023.35</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1664.27</v>
+        <v>1686.43</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3338.52</v>
+        <v>3382.96</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>780.38</v>
+        <v>790.77</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1165.61</v>
+        <v>1181.12</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>887.02</v>
+        <v>898.83</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2087.18</v>
+        <v>2114.96</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>2026.97</v>
+        <v>2053.95</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1011.46</v>
+        <v>1024.92</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2428.01</v>
+        <v>2460.34</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4941.02</v>
+        <v>5006.8</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1271.7</v>
+        <v>1288.63</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>24004.47</v>
+        <v>24324.03</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>4170.91</v>
+        <v>4226.43</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>799.38</v>
+        <v>810.02</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1050.88</v>
+        <v>1064.87</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1853.76</v>
+        <v>1878.44</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>2725.15</v>
+        <v>2761.43</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3047.44</v>
+        <v>3088.01</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1380.77</v>
+        <v>1399.16</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1183.54</v>
+        <v>1199.29</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1163.03</v>
+        <v>1178.51</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1243.89</v>
+        <v>1260.45</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>929.3200000000001</v>
+        <v>941.7</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>3366.02</v>
+        <v>3410.83</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1789.2</v>
+        <v>1813.02</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1254.8</v>
+        <v>1271.5</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1842.75</v>
+        <v>1867.28</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1510.41</v>
+        <v>1530.52</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>798.9400000000001</v>
+        <v>809.5700000000001</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>793.29</v>
+        <v>803.85</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>3378.01</v>
+        <v>3422.98</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>3665.81</v>
+        <v>3713.65</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>4404.3</v>
+        <v>4461.77</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>12608</v>
+        <v>12772.53</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2110.33</v>
+        <v>2137.86</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>10922.82</v>
+        <v>11065.36</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3729.47</v>
+        <v>3778.13</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>839.9</v>
+        <v>850.86</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2545.7</v>
+        <v>2578.92</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>850.54</v>
+        <v>861.64</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>3498.41</v>
+        <v>3544.06</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2986.33</v>
+        <v>3025.3</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1356.06</v>
+        <v>1373.75</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>778.5</v>
+        <v>788.66</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>783.41</v>
+        <v>793.63</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>778.7</v>
+        <v>788.86</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1031.08</v>
+        <v>1044.54</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1604.19</v>
+        <v>1625.12</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>11450.67</v>
+        <v>11600.1</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>6236.8</v>
+        <v>6318.18</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>4494.21</v>
+        <v>4552.86</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>913.95</v>
+        <v>925.88</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>3714.28</v>
+        <v>3762.75</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1769.73</v>
+        <v>1792.82</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2260.19</v>
+        <v>2289.68</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2429.83</v>
+        <v>2461.54</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>4974.58</v>
+        <v>5039.5</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1796.72</v>
+        <v>1820.17</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1472.98</v>
+        <v>1492.2</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>4714.22</v>
+        <v>4775.74</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2039.97</v>
+        <v>2066.59</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>8539.790000000001</v>
+        <v>8651.23</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>963.12</v>
+        <v>975.6900000000001</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>6171.92</v>
+        <v>6252.46</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>2994.31</v>
+        <v>3033.39</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>23974.38</v>
+        <v>24287.24</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1572.25</v>
+        <v>1592.77</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3340.28</v>
+        <v>3383.87</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>2336.57</v>
+        <v>2367.06</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>1421.69</v>
+        <v>1440.24</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>9922.780000000001</v>
+        <v>10052.27</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5930.87</v>
+        <v>6008.27</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>958.3200000000001</v>
+        <v>970.83</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>30665.34</v>
+        <v>31065.51</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1746.53</v>
+        <v>1769.32</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>4321.95</v>
+        <v>4378.35</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>5205.47</v>
+        <v>5333.57</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>917.77</v>
+        <v>940.35</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>25621.53</v>
+        <v>26252.08</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>12196.96</v>
+        <v>12497.12</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1179.95</v>
+        <v>1208.98</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>968.53</v>
+        <v>992.37</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>7555.51</v>
+        <v>7741.45</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1330.78</v>
+        <v>1363.53</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>3610.01</v>
+        <v>3698.85</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>857.59</v>
+        <v>878.6900000000001</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>19235.38</v>
+        <v>19708.76</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3695.46</v>
+        <v>3786.41</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>1146.41</v>
+        <v>1174.63</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>848.7</v>
+        <v>869.59</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>6084.61</v>
+        <v>6234.36</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>789.99</v>
+        <v>809.4299999999999</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1124.84</v>
+        <v>1152.52</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3745.4</v>
+        <v>3837.57</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2255.9</v>
+        <v>2311.42</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>7499.67</v>
+        <v>7684.24</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>832.4299999999999</v>
+        <v>852.91</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2140.42</v>
+        <v>2193.09</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1079.04</v>
+        <v>1105.6</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>4986.97</v>
+        <v>5109.7</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>6563.39</v>
+        <v>6724.91</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>2548.27</v>
+        <v>2610.99</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2628.69</v>
+        <v>2693.38</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1719.77</v>
+        <v>1762.1</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>2597.44</v>
+        <v>2661.36</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>791.46</v>
+        <v>810.9400000000001</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1034.66</v>
+        <v>1060.13</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>925.54</v>
+        <v>948.3200000000001</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>838.6799999999999</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1180.02</v>
+        <v>1209.06</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2885.56</v>
+        <v>2956.57</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2696.79</v>
+        <v>2763.16</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4745.3</v>
+        <v>4862.08</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>988.49</v>
+        <v>1012.82</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>841.74</v>
+        <v>862.46</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>6835.65</v>
+        <v>7003.88</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>7123.58</v>
+        <v>7298.89</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>8182.35</v>
+        <v>8383.719999999999</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>38904.69</v>
+        <v>39862.13</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>849.95</v>
+        <v>866.03</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>3118.33</v>
+        <v>3177.31</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1652.02</v>
+        <v>1683.26</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>1614.26</v>
+        <v>1644.79</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1816.75</v>
+        <v>1851.11</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>1753.6</v>
+        <v>1786.77</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1048.47</v>
+        <v>1068.3</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>962.3099999999999</v>
+        <v>980.51</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>5165.1</v>
+        <v>5262.78</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1669.65</v>
+        <v>1701.23</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1341.9</v>
+        <v>1367.28</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2738.86</v>
+        <v>2790.66</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1074.71</v>
+        <v>1095.04</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>6956.85</v>
+        <v>7088.43</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>3211.79</v>
+        <v>3272.54</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>3408.76</v>
+        <v>3473.23</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>784.29</v>
+        <v>799.13</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1743.21</v>
+        <v>1776.18</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1451.51</v>
+        <v>1478.96</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>4400.03</v>
+        <v>4483.25</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2158.18</v>
+        <v>2198.99</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>1749.52</v>
+        <v>1782.61</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2207.09</v>
+        <v>2248.84</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>11986.67</v>
+        <v>12213.37</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>8082.46</v>
+        <v>8235.32</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>3523.73</v>
+        <v>3590.38</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2679.11</v>
+        <v>2729.78</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>1068.62</v>
+        <v>1088.83</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>986.86</v>
+        <v>1005.52</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1035.69</v>
+        <v>1055.28</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>810.73</v>
+        <v>826.0700000000001</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>1107.87</v>
+        <v>1128.83</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>795.8200000000001</v>
+        <v>810.88</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>4143.02</v>
+        <v>4221.38</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>7442.42</v>
+        <v>7583.17</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3044.36</v>
+        <v>3101.94</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1526.19</v>
+        <v>1555.05</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2922.91</v>
+        <v>2978.19</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1428.88</v>
+        <v>1455.9</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>933.1900000000001</v>
+        <v>950.84</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>3261.83</v>
+        <v>3323.52</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>4615.74</v>
+        <v>4703.04</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2224.67</v>
+        <v>2266.75</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>7636.58</v>
+        <v>7781.01</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>8518.129999999999</v>
+        <v>8679.23</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1551.23</v>
+        <v>1568.88</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>2114.28</v>
+        <v>2138.33</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1205.39</v>
+        <v>1219.1</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1255.91</v>
+        <v>1270.2</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1384.26</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>795.53</v>
+        <v>804.58</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>4108.66</v>
+        <v>4155.39</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1905.16</v>
+        <v>1926.82</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>800.39</v>
+        <v>809.5</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>778.52</v>
+        <v>787.37</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>897.55</v>
+        <v>907.75</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>880.21</v>
+        <v>890.22</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1538.36</v>
+        <v>1555.85</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1187.24</v>
+        <v>1200.74</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>4686.53</v>
+        <v>4739.83</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1716.97</v>
+        <v>1736.5</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1507.18</v>
+        <v>1524.32</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>3139.63</v>
+        <v>3175.34</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>17835.03</v>
+        <v>18037.86</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>4220.42</v>
+        <v>4268.42</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2282.25</v>
+        <v>2308.21</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2699.46</v>
+        <v>2730.15</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>864.54</v>
+        <v>874.37</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>3319.44</v>
+        <v>3357.19</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2149.34</v>
+        <v>2173.78</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1166.16</v>
+        <v>1179.43</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>901.23</v>
+        <v>911.48</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3038.64</v>
+        <v>3073.2</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>830.35</v>
+        <v>839.79</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1450.56</v>
+        <v>1467.05</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>1117.92</v>
+        <v>1130.63</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>799.38</v>
+        <v>808.47</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>946.9299999999999</v>
+        <v>957.6900000000001</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>2241.37</v>
+        <v>2261.56</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1507.08</v>
+        <v>1520.65</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>909.71</v>
+        <v>917.9</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>915.15</v>
+        <v>923.39</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>807.39</v>
+        <v>814.67</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>1314.11</v>
+        <v>1325.95</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>911.1</v>
+        <v>919.3099999999999</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>782.98</v>
+        <v>790.04</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>1063.78</v>
+        <v>1073.36</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>782.26</v>
+        <v>789.3099999999999</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1240.66</v>
+        <v>1251.83</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>1905.41</v>
+        <v>1922.57</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2805.96</v>
+        <v>2831.24</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>5703.09</v>
+        <v>5754.47</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>3842</v>
+        <v>3876.6</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>1862.28</v>
+        <v>1879.06</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2190.37</v>
+        <v>2210.1</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>895.86</v>
+        <v>903.9299999999999</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>3777.03</v>
+        <v>3811.06</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1629.89</v>
+        <v>1644.57</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2087.4</v>
+        <v>2106.21</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1683.31</v>
+        <v>1698.47</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>1322.71</v>
+        <v>1334.63</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>4175.14</v>
+        <v>4212.75</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2981.65</v>
+        <v>3008.51</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>8940.860000000001</v>
+        <v>9021.41</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1779.32</v>
+        <v>1795.35</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>6565.3</v>
+        <v>6624.44</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>927.26</v>
+        <v>935.61</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>812.26</v>
+        <v>819.58</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>3119.95</v>
+        <v>3148.06</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1199.16</v>
+        <v>1209.97</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2011.39</v>
+        <v>2029.51</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>914.48</v>
+        <v>922.72</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1198.3</v>
+        <v>1209.1</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>2695.61</v>
+        <v>2719.89</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2569.69</v>
+        <v>2592.84</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>1039.99</v>
+        <v>1049.36</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>824.92</v>
+        <v>832.35</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>5978.35</v>
+        <v>6032.2</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>870.38</v>
+        <v>878.22</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>1335.62</v>
+        <v>1347.65</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>3461.18</v>
+        <v>3492.36</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>1708.09</v>
+        <v>1723.48</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>2464.86</v>
+        <v>2487.06</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>1319.24</v>
+        <v>1331.12</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>4554.18</v>
+        <v>4595.21</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1113.47</v>
+        <v>1120.59</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>1168.63</v>
+        <v>1176.1</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>998.53</v>
+        <v>1004.92</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>1735.51</v>
+        <v>1746.61</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>1108.48</v>
+        <v>1115.57</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>827.83</v>
+        <v>833.12</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>794.8</v>
+        <v>799.88</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>2519.99</v>
+        <v>2536.11</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1141.31</v>
+        <v>1148.61</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2322.86</v>
+        <v>2337.71</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>5693.64</v>
+        <v>5730.05</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>1282.66</v>
+        <v>1290.86</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>2544.52</v>
+        <v>2560.79</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2141.61</v>
+        <v>2155.31</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1395.02</v>
+        <v>1403.94</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>999.58</v>
+        <v>1005.97</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>1206.62</v>
+        <v>1214.33</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2708.02</v>
+        <v>2725.34</v>
       </c>
     </row>
     <row r="634">
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>192487.36</v>
+        <v>193718.47</v>
       </c>
     </row>
     <row r="635">
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>1106.52</v>
+        <v>1113.6</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>3407.3</v>
+        <v>3429.1</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>6390.53</v>
+        <v>6431.4</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>4671.28</v>
+        <v>4701.15</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>9341.870000000001</v>
+        <v>9371.26</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>792.67</v>
+        <v>795.16</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>1449.3</v>
+        <v>1453.86</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>3299.99</v>
+        <v>3310.37</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>2539.87</v>
+        <v>2547.86</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>1670.22</v>
+        <v>1675.47</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>816.4299999999999</v>
+        <v>819</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>781.95</v>
+        <v>784.41</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>1451.51</v>
+        <v>1456.07</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>6157.29</v>
+        <v>6176.66</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>948.67</v>
+        <v>951.66</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>10025.13</v>
+        <v>10056.67</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>2158.08</v>
+        <v>2164.87</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>10292.12</v>
+        <v>10324.5</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>29006.54</v>
+        <v>29097.81</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>9240.58</v>
+        <v>9269.66</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>780.28</v>
+        <v>782.74</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>847.42</v>
+        <v>850.09</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1917.83</v>
+        <v>1923.87</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>850.2</v>
+        <v>852.88</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1846.39</v>
+        <v>1852.2</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>1917.37</v>
+        <v>1923.4</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>2977.5</v>
+        <v>2986.87</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>3858.58</v>
+        <v>3870.72</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>54643.56</v>
+        <v>54815.49</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>1451.38</v>
+        <v>1455.94</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>3156.22</v>
+        <v>3166.15</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>918.85</v>
+        <v>921.75</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>957.6799999999999</v>
+        <v>960.7</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>1060.56</v>
+        <v>1063.9</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>1756.34</v>
+        <v>1761.86</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>1270.1</v>
+        <v>1274.09</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>791.6</v>
+        <v>794.09</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>786.62</v>
+        <v>789.09</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>948.25</v>
+        <v>951.23</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>782.23</v>
+        <v>784.7</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>806.02</v>
+        <v>809.36</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>3880.23</v>
+        <v>3896.31</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>3326.59</v>
+        <v>3340.38</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>5141.77</v>
+        <v>5163.08</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>3840.97</v>
+        <v>3856.89</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>2227.32</v>
+        <v>2236.55</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>873.1799999999999</v>
+        <v>876.8</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1588.91</v>
+        <v>1595.5</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1203.4</v>
+        <v>1208.39</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>7828.08</v>
+        <v>7860.52</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>1016.61</v>
+        <v>1020.82</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>3585.03</v>
+        <v>3599.89</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1737.91</v>
+        <v>1745.11</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>936.63</v>
+        <v>940.51</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>1557.36</v>
+        <v>1563.82</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>2535.9</v>
+        <v>2546.41</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>792.13</v>
+        <v>795.41</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>1039.74</v>
+        <v>1044.05</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>982.01</v>
+        <v>986.09</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1220.34</v>
+        <v>1225.4</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>6514.15</v>
+        <v>6541.15</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>935.58</v>
+        <v>939.45</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>12920.58</v>
+        <v>12974.14</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>3005.86</v>
+        <v>3018.32</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>7785.02</v>
+        <v>7817.29</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>2966.89</v>
+        <v>2979.19</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>20510.02</v>
+        <v>20595.03</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>2175.27</v>
+        <v>2184.29</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>4303.91</v>
+        <v>4321.75</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>1181.22</v>
+        <v>1186.12</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>1800.67</v>
+        <v>1808.13</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>793.0700000000001</v>
+        <v>796.36</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>11058.63</v>
+        <v>11104.47</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>3034.7</v>
+        <v>3047.28</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>790.3099999999999</v>
+        <v>793.59</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>19300.83</v>
+        <v>19380.82</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>778.9299999999999</v>
+        <v>782.15</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>1682.31</v>
+        <v>1689.29</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>13406.8</v>
+        <v>13462.36</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>4804.52</v>
+        <v>4824.44</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>3232.49</v>
+        <v>3245.89</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>779.29</v>
+        <v>782.52</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2046.44</v>
+        <v>2050.68</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>2648.99</v>
+        <v>2654.48</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>2965.83</v>
+        <v>2971.98</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>907.21</v>
+        <v>909.08</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>796.53</v>
+        <v>798.1799999999999</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>875.3</v>
+        <v>877.12</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>3624.05</v>
+        <v>3631.55</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>2559.12</v>
+        <v>2564.42</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>3850.12</v>
+        <v>3858.1</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>6818.89</v>
+        <v>6833.01</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>1060.4</v>
+        <v>1062.6</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>2304.24</v>
+        <v>2309.01</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>7394.97</v>
+        <v>7410.29</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>963.78</v>
+        <v>965.78</v>
       </c>
     </row>
     <row r="731">
@@ -45046,7 +45046,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>2227.15</v>
+        <v>2231.76</v>
       </c>
     </row>
     <row r="732">
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>3340.69</v>
+        <v>3347.61</v>
       </c>
     </row>
     <row r="733">
@@ -45168,7 +45168,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>867.03</v>
+        <v>868.83</v>
       </c>
     </row>
     <row r="734">
@@ -45229,7 +45229,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>15531.47</v>
+        <v>15563.64</v>
       </c>
     </row>
     <row r="735">
@@ -45290,7 +45290,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>867.03</v>
+        <v>868.83</v>
       </c>
     </row>
     <row r="736">
@@ -45351,7 +45351,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>3295.54</v>
+        <v>3302.37</v>
       </c>
     </row>
     <row r="737">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>955.8099999999999</v>
+        <v>957.79</v>
       </c>
     </row>
     <row r="738">
@@ -45473,7 +45473,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>5865.27</v>
+        <v>5877.42</v>
       </c>
     </row>
     <row r="739">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>10213.04</v>
+        <v>10234.2</v>
       </c>
     </row>
     <row r="740">
@@ -45595,7 +45595,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>38145.39</v>
+        <v>38224.41</v>
       </c>
     </row>
     <row r="741">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>878.63</v>
+        <v>880.45</v>
       </c>
     </row>
     <row r="742">
@@ -45717,7 +45717,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>2415.78</v>
+        <v>2420.79</v>
       </c>
     </row>
     <row r="743">
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>786.8200000000001</v>
+        <v>788.45</v>
       </c>
     </row>
     <row r="744">
@@ -45839,7 +45839,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>20821.77</v>
+        <v>20864.9</v>
       </c>
     </row>
     <row r="745">
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>1658.09</v>
+        <v>1661.53</v>
       </c>
     </row>
     <row r="746">
@@ -45961,7 +45961,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>788</v>
+        <v>789.64</v>
       </c>
     </row>
     <row r="747">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>2780.9</v>
+        <v>2786.66</v>
       </c>
     </row>
     <row r="748">
@@ -46083,7 +46083,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2175.4</v>
+        <v>2179.91</v>
       </c>
     </row>
     <row r="749">
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>1579.87</v>
+        <v>1583.15</v>
       </c>
     </row>
     <row r="750">
@@ -46205,7 +46205,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>1726.91</v>
+        <v>1730.49</v>
       </c>
     </row>
     <row r="751">
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>842.12</v>
+        <v>843.86</v>
       </c>
     </row>
     <row r="752">
@@ -46327,7 +46327,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>780.35</v>
+        <v>781.97</v>
       </c>
     </row>
     <row r="753">
@@ -46388,7 +46388,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>3849.77</v>
+        <v>3857.74</v>
       </c>
     </row>
     <row r="754">
@@ -46449,7 +46449,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>1961.37</v>
+        <v>1965.43</v>
       </c>
     </row>
     <row r="755">
@@ -46510,7 +46510,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>19662.94</v>
+        <v>19703.67</v>
       </c>
     </row>
     <row r="756">
@@ -46571,7 +46571,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>818.67</v>
+        <v>815.15</v>
       </c>
     </row>
     <row r="757">
@@ -46632,7 +46632,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>1249.26</v>
+        <v>1243.89</v>
       </c>
     </row>
     <row r="758">
@@ -46693,7 +46693,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>10125.8</v>
+        <v>10082.31</v>
       </c>
     </row>
     <row r="759">
@@ -46754,7 +46754,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>1019.24</v>
+        <v>1014.86</v>
       </c>
     </row>
     <row r="760">
@@ -46815,7 +46815,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>809.29</v>
+        <v>805.8099999999999</v>
       </c>
     </row>
     <row r="761">
@@ -46876,7 +46876,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>778.4400000000001</v>
+        <v>775.1</v>
       </c>
     </row>
     <row r="762">
@@ -46937,7 +46937,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>843.8</v>
+        <v>840.17</v>
       </c>
     </row>
     <row r="763">
@@ -46998,7 +46998,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>855.5</v>
+        <v>851.83</v>
       </c>
     </row>
     <row r="764">
@@ -47059,7 +47059,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>787.23</v>
+        <v>783.85</v>
       </c>
     </row>
     <row r="765">
@@ -47120,7 +47120,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>2676.51</v>
+        <v>2665.02</v>
       </c>
     </row>
     <row r="766">
@@ -47181,7 +47181,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>1023.87</v>
+        <v>1019.47</v>
       </c>
     </row>
     <row r="767">
@@ -47242,7 +47242,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>12101.69</v>
+        <v>12049.7</v>
       </c>
     </row>
     <row r="768">
@@ -47303,7 +47303,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>3220.14</v>
+        <v>3206.31</v>
       </c>
     </row>
     <row r="769">
@@ -47364,7 +47364,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>3308.52</v>
+        <v>3294.31</v>
       </c>
     </row>
     <row r="770">
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>6511.78</v>
+        <v>6483.8</v>
       </c>
     </row>
     <row r="771">
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>832.23</v>
+        <v>828.65</v>
       </c>
     </row>
     <row r="772">
@@ -47547,7 +47547,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>2997.38</v>
+        <v>2984.5</v>
       </c>
     </row>
     <row r="773">
@@ -47608,7 +47608,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>10293.08</v>
+        <v>10248.86</v>
       </c>
     </row>
     <row r="774">
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>864.62</v>
+        <v>860.91</v>
       </c>
     </row>
     <row r="775">
@@ -47730,7 +47730,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>3536.24</v>
+        <v>3521.05</v>
       </c>
     </row>
     <row r="776">
@@ -47791,7 +47791,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>1598</v>
+        <v>1591.14</v>
       </c>
     </row>
     <row r="777">
@@ -47852,7 +47852,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>849.11</v>
+        <v>845.46</v>
       </c>
     </row>
     <row r="778">
@@ -47913,7 +47913,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>2137.81</v>
+        <v>2128.62</v>
       </c>
     </row>
     <row r="779">
@@ -47974,7 +47974,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>1608.86</v>
+        <v>1601.95</v>
       </c>
     </row>
     <row r="780">
@@ -48035,7 +48035,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>1278.88</v>
+        <v>1273.39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -30199,7 +30199,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32090,7 +32090,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32212,7 +32212,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33493,7 +33493,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33859,7 +33859,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36665,7 +36665,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -39120,7 +39120,7 @@
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
@@ -39536,7 +39536,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40451,7 +40451,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41671,7 +41671,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41793,7 +41793,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -42037,7 +42037,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42891,7 +42891,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -43135,7 +43135,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43684,7 +43684,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -45087,7 +45087,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45392,7 +45392,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45758,7 +45758,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45880,7 +45880,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46612,7 +46612,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46795,7 +46795,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46917,7 +46917,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47100,7 +47100,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47161,7 +47161,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47344,7 +47344,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47405,7 +47405,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47466,7 +47466,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47588,7 +47588,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -47771,7 +47771,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>ILUSTRE MUJNICIPALIDAD DE CAÑETE</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificacion</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERPLAC LOS RIOS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Zonas de Bienestar - Jefatura de Zonas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tribunal Oral en Lo Penal Antofagasta</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Zonas de Bienestar - Jefatura de Zonas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20007,12 +20007,12 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Dirección General de Gendarmería de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Sandra Gioconda Tello López</t>
+          <t>SANDRA GIOCONDA TELLO LÓPEZ</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Sandra Gioconda Tello López</t>
+          <t>SANDRA GIOCONDA TELLO LÓPEZ</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22447,12 +22447,12 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Escuadrilla de Abastecimiento del Edificio FF.AA.</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25070,7 +25070,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25863,7 +25863,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Atacama</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -27022,7 +27022,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27083,7 +27083,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Sandra Gioconda Tello López</t>
+          <t>SANDRA GIOCONDA TELLO LÓPEZ</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27693,7 +27693,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29096,7 +29096,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Clínica Reproducción Humana UV</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -30021,7 +30021,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31292,12 +31292,12 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31353,7 +31353,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31668,7 +31668,7 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
@@ -31719,7 +31719,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -32151,7 +32151,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -32756,7 +32756,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34342,7 +34342,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34464,7 +34464,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -34830,7 +34830,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -34952,7 +34952,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>Municipalidad de Pemuco - Salud</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -35074,7 +35074,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35623,7 +35623,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36233,7 +36233,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36904,7 +36904,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>ADM. FINANCIERO DEL SISTEMA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -36955,7 +36955,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -37758,7 +37758,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38917,7 +38917,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -39714,7 +39714,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -40263,7 +40263,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -40385,7 +40385,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -40446,7 +40446,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -40812,7 +40812,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41117,7 +41117,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>Gendarmeria de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -41178,7 +41178,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -41239,7 +41239,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -41605,7 +41605,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41971,7 +41971,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Delegación Provincial Osorno</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -42642,7 +42642,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -42703,7 +42703,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Delegación Provincial Osorno</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -42764,7 +42764,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
@@ -42886,7 +42886,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -43008,7 +43008,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -43069,7 +43069,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -43252,7 +43252,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -43379,7 +43379,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43440,7 +43440,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43496,7 +43496,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -43618,7 +43618,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -43689,7 +43689,7 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
@@ -43740,7 +43740,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -43862,7 +43862,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -43923,7 +43923,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -44716,7 +44716,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>AP Aquiles</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -44899,7 +44899,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -45143,7 +45143,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -45204,7 +45204,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -45265,7 +45265,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -45631,7 +45631,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -46002,7 +46002,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46302,7 +46302,7 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -46363,7 +46363,7 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -46424,7 +46424,7 @@
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -46485,7 +46485,7 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -46607,7 +46607,7 @@
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -47156,7 +47156,7 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -47888,7 +47888,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -47949,7 +47949,7 @@
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -48010,7 +48010,7 @@
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2037,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2549,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2675,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2866,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2996,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3191,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3256,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3382,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3447,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3703,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3890,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4203,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4333,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4398,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4463,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4528,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4658,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4723,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4788,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4853,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4918,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5296,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5361,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5426,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5552,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5682,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5808,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5873,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5999,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6064,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6251,11 @@
           <t>77.860.046-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6316,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6442,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6568,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6694,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6759,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6824,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6889,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7015,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7080,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7206,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7271,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7401,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7718,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7783,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7913,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8039,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8104,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8295,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8425,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8490,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8555,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8746,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8811,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9071,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9136,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9201,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9518,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9648,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9774,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9839,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9965,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10030,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10095,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10351,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10416,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10481,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10546,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10676,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10802,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10867,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10932,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10997,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11249,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11314,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11749,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11814,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11879,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12009,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12139,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12204,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12269,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12334,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12399,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12464,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12655,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12907,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12972,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13167,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13232,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13297,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13492,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13557,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13683,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13813,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13878,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13943,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14069,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14195,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14260,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14455,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14711,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14776,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15162,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15227,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15292,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15483,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15548,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15678,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15743,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15808,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15873,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15938,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16064,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16129,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16259,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16389,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16515,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16580,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16645,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16710,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16775,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16840,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16905,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +16970,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17035,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17161,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17352,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17417,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17482,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17547,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17673,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17738,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17803,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17929,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +17994,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +18059,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18124,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18189,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18315,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18441,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18506,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18571,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18697,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18762,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18827,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18892,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +18957,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +19022,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19087,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19152,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19217,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19282,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19530,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19595,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19725,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19790,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19855,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +19920,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19985,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20176,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20302,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20367,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20432,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20627,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20757,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20822,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20952,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21139,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +21265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21330,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21460,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21655,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21785,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21850,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21915,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21980,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22171,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22423,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22610,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22736,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22866,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +22931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23183,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23248,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23313,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23504,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23630,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23695,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23760,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23825,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +23951,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24016,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24081,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24146,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24211,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24337,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24402,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24597,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24662,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +24727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +24792,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24857,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +24922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +24987,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +25052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25117,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25182,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25438,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25568,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +25755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +25820,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25885,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +25950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26015,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26141,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26206,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26336,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26401,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26466,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25271,7 +26531,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26661,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26787,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +26852,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26917,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +26982,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27047,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +27112,11 @@
           <t>77.708.749-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27177,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27242,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27307,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27372,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27437,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27502,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27567,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27632,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27697,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27823,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +27949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28014,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28079,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28144,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28270,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28335,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28400,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28526,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28591,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29103,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29168,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29294,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29359,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29424,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29489,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29554,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +29619,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29745,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +29940,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30005,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +30070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30200,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30391,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30647,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +30777,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30842,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31029,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31094,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31350,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31415,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31480,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +31606,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31671,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31736,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31862,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +31988,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32114,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32244,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32309,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32374,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32439,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32504,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32699,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32764,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +32829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +32894,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32959,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33024,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33089,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33154,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33345,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33475,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33601,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +33788,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +33914,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +33979,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34044,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34109,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34174,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34239,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34369,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34434,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34499,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +34564,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +34690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +34755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +34820,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +34946,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35011,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35141,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35389,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35454,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +35584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +35649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +35714,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +35779,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +35844,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +35909,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +35974,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36039,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36104,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36169,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36299,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36364,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36494,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36559,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36624,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +36689,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +36754,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +36819,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +36884,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +37010,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37075,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37140,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37205,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37270,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37335,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37400,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37465,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +37530,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +37595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +37721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +37786,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +37851,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +37916,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37981,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38046,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +38111,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38176,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38367,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38432,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38680,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38745,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +38810,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +38940,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +39005,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39261,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39326,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39391,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39456,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39521,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39586,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39651,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39716,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +39781,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +39846,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39911,11 @@
           <t>77.042.972-2</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39976,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +40041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +40106,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40171,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40236,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40301,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40431,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40496,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40683,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40748,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +41000,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +41065,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39183,7 +41195,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39244,7 +41260,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +41325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +41390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +41455,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39488,7 +41520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +41585,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +41650,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +41715,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39732,7 +41780,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39793,7 +41845,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39854,7 +41910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +41975,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +42101,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40098,7 +42166,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40159,7 +42231,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40220,7 +42296,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40281,7 +42361,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +42426,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40403,7 +42491,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +42556,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +42682,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40647,7 +42747,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40769,7 +42877,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +42942,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +43007,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +43072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +43137,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +43202,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41135,7 +43267,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +43332,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41318,7 +43458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41379,7 +43523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41440,7 +43588,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +43653,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +43718,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +43783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41745,7 +43909,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41806,7 +43974,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +44039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41989,7 +44165,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +44230,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42111,7 +44295,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +44421,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +44486,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42355,7 +44551,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +44616,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42477,7 +44681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +44807,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +44872,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42721,7 +44937,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42782,7 +45002,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42904,7 +45128,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +45193,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43026,7 +45258,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +45384,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43270,7 +45510,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43331,7 +45575,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43453,7 +45701,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43514,7 +45766,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43575,7 +45831,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +45896,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43758,7 +46022,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +46087,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +46152,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44002,7 +46278,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +46343,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44124,7 +46408,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44185,7 +46473,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +46660,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44429,7 +46725,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +46790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +46855,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +46981,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +47046,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44795,7 +47111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44856,7 +47176,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +47241,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +47306,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +47371,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +47436,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +47501,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +47566,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45283,7 +47631,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45344,7 +47696,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45405,7 +47761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47826,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +47891,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45649,7 +48017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45710,7 +48082,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +48147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45832,7 +48212,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +48277,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45954,7 +48342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46015,7 +48407,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +48472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +48537,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +48663,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46320,7 +48728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +48793,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +48858,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46503,7 +48923,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46564,7 +48988,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46686,7 +49114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46747,7 +49179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46808,7 +49244,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46869,7 +49309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46991,7 +49435,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47052,7 +49500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47113,7 +49565,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47174,7 +49630,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47235,7 +49695,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47296,7 +49760,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47357,7 +49825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47418,7 +49890,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47479,7 +49955,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47540,7 +50020,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47601,7 +50085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47662,7 +50150,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47845,7 +50337,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47967,7 +50463,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48028,7 +50528,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/abr-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -20339,7 +20339,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -25475,7 +25475,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -38591,7 +38591,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
@@ -45482,7 +45482,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
@@ -45933,7 +45933,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
